--- a/Collections/EURO/Portugal/#EURO#Portugal#Regular#[2002-present]#circulation_quality.xlsx
+++ b/Collections/EURO/Portugal/#EURO#Portugal#Regular#[2002-present]#circulation_quality.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\EURO\Portugal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D302676D-E0A5-4488-BAE5-BF9C83DDBFC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5BA2665-CEC1-4206-A606-D9D1A265BFAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,6 +46,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -388,7 +391,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="861" uniqueCount="148">
   <si>
     <t>-</t>
   </si>
@@ -601,9 +604,6 @@
     <t>25.029.500</t>
   </si>
   <si>
-    <t>37.572.200</t>
-  </si>
-  <si>
     <t>220.359.835</t>
   </si>
   <si>
@@ -622,9 +622,6 @@
     <t>10.038.000</t>
   </si>
   <si>
-    <t>19.331.000</t>
-  </si>
-  <si>
     <t>147.481.038</t>
   </si>
   <si>
@@ -637,9 +634,6 @@
     <t>20.038.000</t>
   </si>
   <si>
-    <t>15.027.000</t>
-  </si>
-  <si>
     <t>152.017.133</t>
   </si>
   <si>
@@ -691,9 +685,6 @@
     <t>20.034.500</t>
   </si>
   <si>
-    <t>25.032.000</t>
-  </si>
-  <si>
     <t>62.000.775</t>
   </si>
   <si>
@@ -715,51 +706,9 @@
     <t>Obv: The royal seal of 1144</t>
   </si>
   <si>
-    <t>15.500</t>
-  </si>
-  <si>
     <t>50.025.500</t>
   </si>
   <si>
-    <t>25.500</t>
-  </si>
-  <si>
-    <t>30.025.500</t>
-  </si>
-  <si>
-    <t>20.025.500</t>
-  </si>
-  <si>
-    <t>10.025.500</t>
-  </si>
-  <si>
-    <t>18.000</t>
-  </si>
-  <si>
-    <t>4.028.000</t>
-  </si>
-  <si>
-    <t>15.000</t>
-  </si>
-  <si>
-    <t>15.015.000</t>
-  </si>
-  <si>
-    <t>10.015.000</t>
-  </si>
-  <si>
-    <t>20.015.000</t>
-  </si>
-  <si>
-    <t>17.500</t>
-  </si>
-  <si>
-    <t>25.000</t>
-  </si>
-  <si>
-    <t>28.000</t>
-  </si>
-  <si>
     <t>Obv: The royal seal of 1145</t>
   </si>
   <si>
@@ -791,6 +740,102 @@
   </si>
   <si>
     <t>Subtype_2#Map_of_Europe</t>
+  </si>
+  <si>
+    <t>50.016.462</t>
+  </si>
+  <si>
+    <t>14.036</t>
+  </si>
+  <si>
+    <t>37.559.236</t>
+  </si>
+  <si>
+    <t>19.318.036</t>
+  </si>
+  <si>
+    <t>15.014.036</t>
+  </si>
+  <si>
+    <t>25.015.766</t>
+  </si>
+  <si>
+    <t>9.822</t>
+  </si>
+  <si>
+    <t>30.009.822</t>
+  </si>
+  <si>
+    <t>20.009.822</t>
+  </si>
+  <si>
+    <t>10.009.822</t>
+  </si>
+  <si>
+    <t>4.011.743</t>
+  </si>
+  <si>
+    <t>16.462</t>
+  </si>
+  <si>
+    <t>15.016.462</t>
+  </si>
+  <si>
+    <t>30.017.990</t>
+  </si>
+  <si>
+    <t>13.165</t>
+  </si>
+  <si>
+    <t>15.013.165</t>
+  </si>
+  <si>
+    <t>10.013.165</t>
+  </si>
+  <si>
+    <t>20.013.165</t>
+  </si>
+  <si>
+    <t>15.182</t>
+  </si>
+  <si>
+    <t>12.350</t>
+  </si>
+  <si>
+    <t>14.824</t>
+  </si>
+  <si>
+    <t>55.011.199</t>
+  </si>
+  <si>
+    <t>11.199</t>
+  </si>
+  <si>
+    <t>40.011.199</t>
+  </si>
+  <si>
+    <t>13.532</t>
+  </si>
+  <si>
+    <t>15.011.199</t>
+  </si>
+  <si>
+    <t>8.601</t>
+  </si>
+  <si>
+    <t>40.008.601</t>
+  </si>
+  <si>
+    <t>30.008.601</t>
+  </si>
+  <si>
+    <t>20.010.834</t>
+  </si>
+  <si>
+    <t>9.700</t>
+  </si>
+  <si>
+    <t>12.700</t>
   </si>
 </sst>
 </file>
@@ -1093,10 +1138,10 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1105,15 +1150,14 @@
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
-  <dxfs count="25">
+  <dxfs count="52">
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -1291,6 +1335,223 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -1322,9 +1583,9 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="1" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="51"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="50" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="49"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -1593,7 +1854,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -1624,13 +1885,13 @@
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="28"/>
       <c r="B2" s="26" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>28</v>
@@ -1645,7 +1906,7 @@
         <v>2002</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C3" s="12" t="s">
         <v>29</v>
@@ -1668,7 +1929,7 @@
         <v>2003</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>29</v>
@@ -1691,7 +1952,7 @@
         <v>2004</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>29</v>
@@ -1713,7 +1974,7 @@
         <v>2005</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>29</v>
@@ -1735,7 +1996,7 @@
         <v>2006</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>29</v>
@@ -1757,7 +2018,7 @@
         <v>2007</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>29</v>
@@ -1779,7 +2040,7 @@
         <v>2008</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>29</v>
@@ -1801,7 +2062,7 @@
         <v>2009</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C10" s="12" t="s">
         <v>29</v>
@@ -1823,7 +2084,7 @@
         <v>2010</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>29</v>
@@ -1845,7 +2106,7 @@
         <v>2011</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C12" s="12" t="s">
         <v>29</v>
@@ -1867,7 +2128,7 @@
         <v>2012</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C13" s="12" t="s">
         <v>29</v>
@@ -1889,7 +2150,7 @@
         <v>2013</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C14" s="12" t="s">
         <v>29</v>
@@ -1911,7 +2172,7 @@
         <v>2014</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C15" s="12" t="s">
         <v>29</v>
@@ -1933,7 +2194,7 @@
         <v>2015</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C16" s="12" t="s">
         <v>29</v>
@@ -1955,7 +2216,7 @@
         <v>2016</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C17" s="12" t="s">
         <v>29</v>
@@ -1977,7 +2238,7 @@
         <v>2017</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C18" s="12" t="s">
         <v>29</v>
@@ -1999,7 +2260,7 @@
         <v>2018</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C19" s="12" t="s">
         <v>29</v>
@@ -2021,14 +2282,14 @@
         <v>2019</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C20" s="12" t="s">
         <v>29</v>
       </c>
       <c r="D20" s="12"/>
       <c r="E20" s="13" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
@@ -2043,16 +2304,16 @@
         <v>2020</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C21" s="12" t="s">
         <v>29</v>
       </c>
       <c r="D21" s="12"/>
-      <c r="E21" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="F21" s="1" t="s">
+      <c r="E21" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="F21" s="1">
         <v>0</v>
       </c>
       <c r="G21" s="3" t="str">
@@ -2065,14 +2326,14 @@
         <v>2021</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="C22" s="12" t="s">
         <v>29</v>
       </c>
       <c r="D22" s="12"/>
       <c r="E22" s="24" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>0</v>
@@ -2087,14 +2348,14 @@
         <v>2022</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="C23" s="12" t="s">
         <v>29</v>
       </c>
       <c r="D23" s="12"/>
       <c r="E23" s="24" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>0</v>
@@ -2109,22 +2370,60 @@
         <v>2023</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="C24" s="12" t="s">
         <v>29</v>
       </c>
       <c r="D24" s="12"/>
-      <c r="E24" s="24" t="s">
-        <v>121</v>
-      </c>
-      <c r="F24" s="1" t="s">
+      <c r="E24" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="F24" s="1">
         <v>0</v>
       </c>
       <c r="G24" s="3" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
+    </row>
+    <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="10">
+        <v>2024</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D25" s="12"/>
+      <c r="E25" s="24" t="s">
+        <v>142</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G25" s="3"/>
+    </row>
+    <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="10">
+        <v>2025</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D26" s="12"/>
+      <c r="E26" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3"/>
     </row>
   </sheetData>
   <autoFilter ref="B2:E2" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -2133,12 +2432,46 @@
     <mergeCell ref="C1:D1"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
-  <conditionalFormatting sqref="F3:F20">
-    <cfRule type="containsText" dxfId="24" priority="5" operator="containsText" text="*-">
+  <conditionalFormatting sqref="F3:F21">
+    <cfRule type="containsText" dxfId="48" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F3:F20">
+  <conditionalFormatting sqref="F3:F21">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F22:F23">
+    <cfRule type="containsText" dxfId="47" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F22))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F22:F23">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F24">
+    <cfRule type="containsText" dxfId="26" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F24))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F24">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2150,12 +2483,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F21:F24">
+  <conditionalFormatting sqref="F25:F26">
     <cfRule type="containsText" dxfId="23" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F21:F24">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F25))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F25:F26">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2175,7 +2508,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -2206,13 +2539,13 @@
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="28"/>
       <c r="B2" s="26" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>28</v>
@@ -2227,7 +2560,7 @@
         <v>2002</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C3" s="12" t="s">
         <v>29</v>
@@ -2250,7 +2583,7 @@
         <v>2003</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>29</v>
@@ -2273,7 +2606,7 @@
         <v>2004</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>29</v>
@@ -2295,7 +2628,7 @@
         <v>2005</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>29</v>
@@ -2317,7 +2650,7 @@
         <v>2006</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>29</v>
@@ -2339,7 +2672,7 @@
         <v>2007</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>29</v>
@@ -2361,7 +2694,7 @@
         <v>2008</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>29</v>
@@ -2383,7 +2716,7 @@
         <v>2009</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C10" s="12" t="s">
         <v>29</v>
@@ -2405,7 +2738,7 @@
         <v>2010</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>29</v>
@@ -2427,7 +2760,7 @@
         <v>2011</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C12" s="12" t="s">
         <v>29</v>
@@ -2449,7 +2782,7 @@
         <v>2012</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C13" s="12" t="s">
         <v>29</v>
@@ -2471,7 +2804,7 @@
         <v>2013</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C14" s="12" t="s">
         <v>29</v>
@@ -2493,7 +2826,7 @@
         <v>2014</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C15" s="12" t="s">
         <v>29</v>
@@ -2515,7 +2848,7 @@
         <v>2015</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C16" s="12" t="s">
         <v>29</v>
@@ -2537,7 +2870,7 @@
         <v>2016</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C17" s="12" t="s">
         <v>29</v>
@@ -2559,7 +2892,7 @@
         <v>2017</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C18" s="12" t="s">
         <v>29</v>
@@ -2581,14 +2914,14 @@
         <v>2018</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C19" s="12" t="s">
         <v>29</v>
       </c>
       <c r="D19" s="6"/>
       <c r="E19" s="24" t="s">
-        <v>45</v>
+        <v>117</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>0</v>
@@ -2603,14 +2936,14 @@
         <v>2019</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C20" s="12" t="s">
         <v>29</v>
       </c>
       <c r="D20" s="6"/>
       <c r="E20" s="24" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>0</v>
@@ -2625,14 +2958,14 @@
         <v>2020</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C21" s="12" t="s">
         <v>29</v>
       </c>
       <c r="D21" s="6"/>
       <c r="E21" s="24" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>0</v>
@@ -2647,14 +2980,14 @@
         <v>2021</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C22" s="12" t="s">
         <v>29</v>
       </c>
       <c r="D22" s="6"/>
       <c r="E22" s="24" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>0</v>
@@ -2669,14 +3002,14 @@
         <v>2022</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C23" s="12" t="s">
         <v>29</v>
       </c>
       <c r="D23" s="6"/>
       <c r="E23" s="24" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>0</v>
@@ -2691,20 +3024,64 @@
         <v>2023</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C24" s="12" t="s">
         <v>29</v>
       </c>
       <c r="D24" s="6"/>
       <c r="E24" s="24" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G24" s="3" t="str">
         <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="10">
+        <v>2024</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D25" s="6"/>
+      <c r="E25" s="24" t="s">
+        <v>142</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G25" s="3" t="str">
+        <f t="shared" ref="G25:G26" si="3">IF(OR(AND(F25&gt;1,F25&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="10">
+        <v>2025</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D26" s="6"/>
+      <c r="E26" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3" t="str">
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -2716,11 +3093,28 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="F3:F20 F22 F24">
-    <cfRule type="containsText" dxfId="22" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="46" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F20 F22 F24">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F21 F23">
+    <cfRule type="containsText" dxfId="45" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F23 F21">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2732,12 +3126,29 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F21 F23">
+  <conditionalFormatting sqref="F26">
+    <cfRule type="containsText" dxfId="22" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F26))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F26">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F25">
     <cfRule type="containsText" dxfId="21" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F23 F21">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F25))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F25">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2757,7 +3168,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -2788,13 +3199,13 @@
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="28"/>
       <c r="B2" s="26" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>28</v>
@@ -2809,7 +3220,7 @@
         <v>2002</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C3" s="12" t="s">
         <v>29</v>
@@ -2832,7 +3243,7 @@
         <v>2003</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>29</v>
@@ -2855,7 +3266,7 @@
         <v>2004</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>29</v>
@@ -2877,7 +3288,7 @@
         <v>2005</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>29</v>
@@ -2899,7 +3310,7 @@
         <v>2006</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>29</v>
@@ -2921,7 +3332,7 @@
         <v>2007</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>29</v>
@@ -2943,7 +3354,7 @@
         <v>2008</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>29</v>
@@ -2965,7 +3376,7 @@
         <v>2009</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C10" s="12" t="s">
         <v>29</v>
@@ -2987,7 +3398,7 @@
         <v>2010</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>29</v>
@@ -3009,7 +3420,7 @@
         <v>2011</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C12" s="12" t="s">
         <v>29</v>
@@ -3031,7 +3442,7 @@
         <v>2012</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C13" s="12" t="s">
         <v>29</v>
@@ -3053,7 +3464,7 @@
         <v>2013</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C14" s="12" t="s">
         <v>29</v>
@@ -3075,7 +3486,7 @@
         <v>2014</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C15" s="12" t="s">
         <v>29</v>
@@ -3097,7 +3508,7 @@
         <v>2015</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C16" s="12" t="s">
         <v>29</v>
@@ -3119,7 +3530,7 @@
         <v>2016</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C17" s="12" t="s">
         <v>29</v>
@@ -3141,7 +3552,7 @@
         <v>2017</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C18" s="12" t="s">
         <v>29</v>
@@ -3163,14 +3574,14 @@
         <v>2018</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C19" s="12" t="s">
         <v>29</v>
       </c>
       <c r="D19" s="6"/>
       <c r="E19" s="13" t="s">
-        <v>70</v>
+        <v>118</v>
       </c>
       <c r="F19" s="1">
         <v>0</v>
@@ -3185,14 +3596,14 @@
         <v>2019</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C20" s="12" t="s">
         <v>29</v>
       </c>
       <c r="D20" s="6"/>
       <c r="E20" s="13" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
@@ -3207,14 +3618,14 @@
         <v>2020</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C21" s="12" t="s">
         <v>29</v>
       </c>
       <c r="D21" s="6"/>
       <c r="E21" s="24" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>0</v>
@@ -3229,20 +3640,20 @@
         <v>2021</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="C22" s="12" t="s">
         <v>29</v>
       </c>
       <c r="D22" s="6"/>
       <c r="E22" s="13" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
       </c>
       <c r="G22" s="3" t="str">
-        <f t="shared" ref="G22:G24" si="2">IF(OR(AND(F22&gt;1,F22&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="G22:G26" si="2">IF(OR(AND(F22&gt;1,F22&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -3251,14 +3662,14 @@
         <v>2022</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="C23" s="12" t="s">
         <v>29</v>
       </c>
       <c r="D23" s="6"/>
       <c r="E23" s="24" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>0</v>
@@ -3273,19 +3684,63 @@
         <v>2023</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="C24" s="12" t="s">
         <v>29</v>
       </c>
       <c r="D24" s="6"/>
-      <c r="E24" s="24" t="s">
-        <v>121</v>
-      </c>
-      <c r="F24" s="1" t="s">
+      <c r="E24" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="F24" s="1">
         <v>0</v>
       </c>
       <c r="G24" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="10">
+        <v>2024</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D25" s="6"/>
+      <c r="E25" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="F25" s="1">
+        <v>0</v>
+      </c>
+      <c r="G25" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="10">
+        <v>2025</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D26" s="6"/>
+      <c r="E26" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -3298,11 +3753,62 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="F3:F20">
+    <cfRule type="containsText" dxfId="44" priority="15" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3:F20">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F21 F23">
+    <cfRule type="containsText" dxfId="43" priority="11" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F21 F23">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F22">
+    <cfRule type="containsText" dxfId="42" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F22))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F22">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F26">
     <cfRule type="containsText" dxfId="20" priority="7" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F3:F20">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F26))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F26">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3314,12 +3820,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F21 F23:F24">
-    <cfRule type="containsText" dxfId="19" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F23:F24 F21">
+  <conditionalFormatting sqref="F24">
+    <cfRule type="containsText" dxfId="8" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F24))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F24">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3331,12 +3837,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F22">
-    <cfRule type="containsText" dxfId="18" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F22))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F22">
+  <conditionalFormatting sqref="F25">
+    <cfRule type="containsText" dxfId="7" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F25))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F25">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3356,7 +3862,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -3375,7 +3881,7 @@
       <c r="C1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="32"/>
+      <c r="D1" s="33"/>
       <c r="E1" s="8" t="s">
         <v>3</v>
       </c>
@@ -3385,15 +3891,15 @@
       <c r="G1" s="2"/>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="33"/>
+      <c r="A2" s="32"/>
       <c r="B2" s="26" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>28</v>
@@ -3408,7 +3914,7 @@
         <v>2002</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C3" s="12" t="s">
         <v>29</v>
@@ -3417,7 +3923,7 @@
         <v>8</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F3" s="1">
         <v>2</v>
@@ -3432,7 +3938,7 @@
         <v>2003</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>29</v>
@@ -3441,7 +3947,7 @@
         <v>8</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F4" s="1">
         <v>0</v>
@@ -3456,7 +3962,7 @@
         <v>2004</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>29</v>
@@ -3480,7 +3986,7 @@
         <v>2005</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>29</v>
@@ -3489,7 +3995,7 @@
         <v>8</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F6" s="1">
         <v>0</v>
@@ -3504,7 +4010,7 @@
         <v>2006</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>29</v>
@@ -3528,7 +4034,7 @@
         <v>2007</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>29</v>
@@ -3537,7 +4043,7 @@
         <v>8</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>0</v>
@@ -3552,7 +4058,7 @@
         <v>2008</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>29</v>
@@ -3561,7 +4067,7 @@
         <v>9</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F9" s="1">
         <v>0</v>
@@ -3576,7 +4082,7 @@
         <v>2009</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C10" s="12" t="s">
         <v>29</v>
@@ -3585,7 +4091,7 @@
         <v>9</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F10" s="1">
         <v>0</v>
@@ -3600,7 +4106,7 @@
         <v>2010</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>29</v>
@@ -3624,7 +4130,7 @@
         <v>2011</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C12" s="12" t="s">
         <v>29</v>
@@ -3648,7 +4154,7 @@
         <v>2012</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C13" s="12" t="s">
         <v>29</v>
@@ -3672,7 +4178,7 @@
         <v>2013</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C14" s="12" t="s">
         <v>29</v>
@@ -3696,7 +4202,7 @@
         <v>2014</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C15" s="12" t="s">
         <v>29</v>
@@ -3720,7 +4226,7 @@
         <v>2015</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C16" s="12" t="s">
         <v>29</v>
@@ -3744,7 +4250,7 @@
         <v>2016</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C17" s="12" t="s">
         <v>29</v>
@@ -3768,7 +4274,7 @@
         <v>2017</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C18" s="12" t="s">
         <v>29</v>
@@ -3792,7 +4298,7 @@
         <v>2018</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C19" s="12" t="s">
         <v>29</v>
@@ -3801,7 +4307,7 @@
         <v>9</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>77</v>
+        <v>119</v>
       </c>
       <c r="F19" s="1">
         <v>0</v>
@@ -3816,7 +4322,7 @@
         <v>2019</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C20" s="12" t="s">
         <v>29</v>
@@ -3825,7 +4331,7 @@
         <v>9</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
@@ -3840,7 +4346,7 @@
         <v>2020</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C21" s="12" t="s">
         <v>29</v>
@@ -3849,7 +4355,7 @@
         <v>9</v>
       </c>
       <c r="E21" s="24" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>0</v>
@@ -3864,7 +4370,7 @@
         <v>2021</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="C22" s="12" t="s">
         <v>29</v>
@@ -3872,10 +4378,10 @@
       <c r="D22" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E22" s="24" t="s">
-        <v>117</v>
-      </c>
-      <c r="F22" s="1" t="s">
+      <c r="E22" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="F22" s="1">
         <v>0</v>
       </c>
       <c r="G22" s="3" t="str">
@@ -3888,7 +4394,7 @@
         <v>2022</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C23" s="12" t="s">
         <v>29</v>
@@ -3896,10 +4402,10 @@
       <c r="D23" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E23" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="F23" s="1">
+      <c r="E23" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="F23" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G23" s="3" t="str">
@@ -3912,7 +4418,7 @@
         <v>2023</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="C24" s="12" t="s">
         <v>29</v>
@@ -3921,13 +4427,61 @@
         <v>9</v>
       </c>
       <c r="E24" s="24" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G24" s="3" t="str">
-        <f t="shared" ref="G24" si="3">IF(OR(AND(F24&gt;1,F24&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="G24:G26" si="3">IF(OR(AND(F24&gt;1,F24&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="10">
+        <v>2024</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="F25" s="1">
+        <v>0</v>
+      </c>
+      <c r="G25" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="10">
+        <v>2025</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3" t="str">
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -3939,12 +4493,12 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="F3:F20">
-    <cfRule type="containsText" dxfId="17" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="41" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F20">
-    <cfRule type="colorScale" priority="8">
+    <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -3955,12 +4509,63 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F21:F22 F24">
-    <cfRule type="containsText" dxfId="16" priority="3" operator="containsText" text="*-">
+  <conditionalFormatting sqref="F21 F24">
+    <cfRule type="containsText" dxfId="40" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F21:F22 F24">
+  <conditionalFormatting sqref="F24 F21">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F26">
+    <cfRule type="containsText" dxfId="18" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F26))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F26">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F22">
+    <cfRule type="containsText" dxfId="6" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F22))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F22">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F25">
+    <cfRule type="containsText" dxfId="5" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F25))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F25">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3973,7 +4578,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F23">
-    <cfRule type="containsText" dxfId="15" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F23))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3997,7 +4602,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -4016,7 +4621,7 @@
       <c r="C1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="32"/>
+      <c r="D1" s="33"/>
       <c r="E1" s="8" t="s">
         <v>3</v>
       </c>
@@ -4026,15 +4631,15 @@
       <c r="G1" s="2"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="33"/>
+      <c r="A2" s="32"/>
       <c r="B2" s="26" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>28</v>
@@ -4049,7 +4654,7 @@
         <v>2002</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C3" s="12" t="s">
         <v>29</v>
@@ -4058,7 +4663,7 @@
         <v>8</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F3" s="1">
         <v>1</v>
@@ -4074,7 +4679,7 @@
         <v>2003</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>29</v>
@@ -4083,7 +4688,7 @@
         <v>8</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F4" s="1">
         <v>0</v>
@@ -4099,7 +4704,7 @@
         <v>2004</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>29</v>
@@ -4123,7 +4728,7 @@
         <v>2005</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>29</v>
@@ -4132,7 +4737,7 @@
         <v>8</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F6" s="1">
         <v>0</v>
@@ -4147,7 +4752,7 @@
         <v>2006</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>29</v>
@@ -4171,7 +4776,7 @@
         <v>2007</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>29</v>
@@ -4180,7 +4785,7 @@
         <v>8</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>0</v>
@@ -4195,7 +4800,7 @@
         <v>2008</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>29</v>
@@ -4204,7 +4809,7 @@
         <v>9</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F9" s="1">
         <v>0</v>
@@ -4219,7 +4824,7 @@
         <v>2009</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C10" s="12" t="s">
         <v>29</v>
@@ -4228,7 +4833,7 @@
         <v>9</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F10" s="1">
         <v>1</v>
@@ -4243,7 +4848,7 @@
         <v>2010</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>29</v>
@@ -4267,7 +4872,7 @@
         <v>2011</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C12" s="12" t="s">
         <v>29</v>
@@ -4291,7 +4896,7 @@
         <v>2012</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C13" s="12" t="s">
         <v>29</v>
@@ -4315,7 +4920,7 @@
         <v>2013</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C14" s="12" t="s">
         <v>29</v>
@@ -4339,7 +4944,7 @@
         <v>2014</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C15" s="12" t="s">
         <v>29</v>
@@ -4363,7 +4968,7 @@
         <v>2015</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C16" s="12" t="s">
         <v>29</v>
@@ -4387,7 +4992,7 @@
         <v>2016</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C17" s="12" t="s">
         <v>29</v>
@@ -4411,7 +5016,7 @@
         <v>2017</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C18" s="12" t="s">
         <v>29</v>
@@ -4435,7 +5040,7 @@
         <v>2018</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C19" s="12" t="s">
         <v>29</v>
@@ -4444,7 +5049,7 @@
         <v>9</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="F19" s="1">
         <v>0</v>
@@ -4459,7 +5064,7 @@
         <v>2019</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C20" s="12" t="s">
         <v>29</v>
@@ -4468,7 +5073,7 @@
         <v>9</v>
       </c>
       <c r="E20" s="24" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>0</v>
@@ -4483,7 +5088,7 @@
         <v>2020</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C21" s="12" t="s">
         <v>29</v>
@@ -4491,10 +5096,10 @@
       <c r="D21" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E21" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="F21" s="1" t="s">
+      <c r="E21" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="F21" s="1">
         <v>0</v>
       </c>
       <c r="G21" s="3" t="str">
@@ -4507,7 +5112,7 @@
         <v>2021</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="C22" s="12" t="s">
         <v>29</v>
@@ -4516,13 +5121,13 @@
         <v>9</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
       </c>
       <c r="G22" s="3" t="str">
-        <f t="shared" ref="G22:G24" si="2">IF(OR(AND(F22&gt;1,F22&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="G22:G26" si="2">IF(OR(AND(F22&gt;1,F22&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -4531,7 +5136,7 @@
         <v>2022</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C23" s="12" t="s">
         <v>29</v>
@@ -4540,7 +5145,7 @@
         <v>9</v>
       </c>
       <c r="E23" s="24" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>0</v>
@@ -4555,7 +5160,7 @@
         <v>2023</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="C24" s="12" t="s">
         <v>29</v>
@@ -4564,12 +5169,60 @@
         <v>9</v>
       </c>
       <c r="E24" s="24" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G24" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="10">
+        <v>2024</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="F25" s="1">
+        <v>0</v>
+      </c>
+      <c r="G25" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="10">
+        <v>2025</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -4582,11 +5235,62 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="F3:F20">
-    <cfRule type="containsText" dxfId="14" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="38" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F20">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F23:F24">
+    <cfRule type="containsText" dxfId="37" priority="11" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F23))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F23:F24">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F22">
+    <cfRule type="containsText" dxfId="36" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F22))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F22">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F26">
+    <cfRule type="containsText" dxfId="16" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F26))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F26">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4598,12 +5302,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F21 F23:F24">
-    <cfRule type="containsText" dxfId="13" priority="3" operator="containsText" text="*-">
+  <conditionalFormatting sqref="F21">
+    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F23:F24 F21">
+  <conditionalFormatting sqref="F21">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4615,12 +5319,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F22">
-    <cfRule type="containsText" dxfId="12" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F22))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F22">
+  <conditionalFormatting sqref="F25">
+    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F25))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F25">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4659,7 +5363,7 @@
       <c r="C1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="32"/>
+      <c r="D1" s="33"/>
       <c r="E1" s="8" t="s">
         <v>3</v>
       </c>
@@ -4669,15 +5373,15 @@
       <c r="G1" s="2"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="33"/>
+      <c r="A2" s="32"/>
       <c r="B2" s="26" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>28</v>
@@ -4692,7 +5396,7 @@
         <v>2002</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C3" s="12" t="s">
         <v>29</v>
@@ -4701,7 +5405,7 @@
         <v>8</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F3" s="1">
         <v>3</v>
@@ -4717,7 +5421,7 @@
         <v>2003</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>29</v>
@@ -4726,7 +5430,7 @@
         <v>8</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F4" s="1">
         <v>0</v>
@@ -4742,7 +5446,7 @@
         <v>2004</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>29</v>
@@ -4766,7 +5470,7 @@
         <v>2005</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>29</v>
@@ -4775,7 +5479,7 @@
         <v>8</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F6" s="1">
         <v>0</v>
@@ -4790,7 +5494,7 @@
         <v>2006</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>29</v>
@@ -4814,7 +5518,7 @@
         <v>2007</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>29</v>
@@ -4823,7 +5527,7 @@
         <v>8</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>0</v>
@@ -4838,7 +5542,7 @@
         <v>2008</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>29</v>
@@ -4847,7 +5551,7 @@
         <v>9</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F9" s="1">
         <v>0</v>
@@ -4862,7 +5566,7 @@
         <v>2009</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C10" s="12" t="s">
         <v>29</v>
@@ -4871,7 +5575,7 @@
         <v>9</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F10" s="1">
         <v>0</v>
@@ -4886,7 +5590,7 @@
         <v>2010</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>29</v>
@@ -4910,7 +5614,7 @@
         <v>2011</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C12" s="12" t="s">
         <v>29</v>
@@ -4934,7 +5638,7 @@
         <v>2012</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C13" s="12" t="s">
         <v>29</v>
@@ -4958,7 +5662,7 @@
         <v>2013</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C14" s="12" t="s">
         <v>29</v>
@@ -4982,7 +5686,7 @@
         <v>2014</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C15" s="12" t="s">
         <v>29</v>
@@ -5006,7 +5710,7 @@
         <v>2015</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C16" s="12" t="s">
         <v>29</v>
@@ -5030,7 +5734,7 @@
         <v>2016</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C17" s="12" t="s">
         <v>29</v>
@@ -5039,7 +5743,7 @@
         <v>9</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F17" s="1">
         <v>0</v>
@@ -5054,7 +5758,7 @@
         <v>2017</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C18" s="12" t="s">
         <v>29</v>
@@ -5078,7 +5782,7 @@
         <v>2018</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C19" s="12" t="s">
         <v>29</v>
@@ -5087,7 +5791,7 @@
         <v>9</v>
       </c>
       <c r="E19" s="24" t="s">
-        <v>45</v>
+        <v>117</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>0</v>
@@ -5102,7 +5806,7 @@
         <v>2019</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C20" s="12" t="s">
         <v>29</v>
@@ -5111,7 +5815,7 @@
         <v>9</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
@@ -5126,7 +5830,7 @@
         <v>2020</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C21" s="12" t="s">
         <v>29</v>
@@ -5135,7 +5839,7 @@
         <v>9</v>
       </c>
       <c r="E21" s="24" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>0</v>
@@ -5150,7 +5854,7 @@
         <v>2021</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="C22" s="12" t="s">
         <v>29</v>
@@ -5159,13 +5863,13 @@
         <v>9</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
       </c>
       <c r="G22" s="3" t="str">
-        <f t="shared" ref="G22:G24" si="2">IF(OR(AND(F22&gt;1,F22&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="G22:G26" si="2">IF(OR(AND(F22&gt;1,F22&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -5174,7 +5878,7 @@
         <v>2022</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C23" s="12" t="s">
         <v>29</v>
@@ -5183,7 +5887,7 @@
         <v>9</v>
       </c>
       <c r="E23" s="24" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>0</v>
@@ -5198,7 +5902,7 @@
         <v>2023</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="C24" s="12" t="s">
         <v>29</v>
@@ -5207,7 +5911,7 @@
         <v>9</v>
       </c>
       <c r="E24" s="24" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>0</v>
@@ -5217,7 +5921,53 @@
         <v/>
       </c>
     </row>
+    <row r="25" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="10">
+        <v>2024</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E25" s="24" t="s">
+        <v>142</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G25" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
     <row r="26" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="10">
+        <v>2025</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
       <c r="S26" s="25"/>
     </row>
   </sheetData>
@@ -5228,11 +5978,28 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="F3:F20">
-    <cfRule type="containsText" dxfId="11" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="35" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F20">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F21 F23:F24">
+    <cfRule type="containsText" dxfId="34" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F23:F24 F21">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5244,12 +6011,29 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F21 F23:F24">
-    <cfRule type="containsText" dxfId="10" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F23:F24 F21">
+  <conditionalFormatting sqref="F22">
+    <cfRule type="containsText" dxfId="33" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F22))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F22">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F26">
+    <cfRule type="containsText" dxfId="14" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F26))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F26">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5261,12 +6045,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F22">
-    <cfRule type="containsText" dxfId="9" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F22))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F22">
+  <conditionalFormatting sqref="F25">
+    <cfRule type="containsText" dxfId="13" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F25))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F25">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5286,7 +6070,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -5305,7 +6089,7 @@
       <c r="C1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="32"/>
+      <c r="D1" s="33"/>
       <c r="E1" s="8" t="s">
         <v>3</v>
       </c>
@@ -5315,15 +6099,15 @@
       <c r="G1" s="2"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="33"/>
+      <c r="A2" s="32"/>
       <c r="B2" s="26" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>28</v>
@@ -5338,7 +6122,7 @@
         <v>2002</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C3" s="12" t="s">
         <v>29</v>
@@ -5347,7 +6131,7 @@
         <v>8</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F3" s="1">
         <v>0</v>
@@ -5363,7 +6147,7 @@
         <v>2003</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>29</v>
@@ -5372,7 +6156,7 @@
         <v>8</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F4" s="1">
         <v>1</v>
@@ -5389,7 +6173,7 @@
         <v>2004</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>29</v>
@@ -5398,7 +6182,7 @@
         <v>8</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
@@ -5413,7 +6197,7 @@
         <v>2005</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>29</v>
@@ -5422,7 +6206,7 @@
         <v>8</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
@@ -5437,7 +6221,7 @@
         <v>2006</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>29</v>
@@ -5461,7 +6245,7 @@
         <v>2007</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>29</v>
@@ -5470,7 +6254,7 @@
         <v>8</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F8" s="1">
         <v>0</v>
@@ -5485,7 +6269,7 @@
         <v>2008</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>29</v>
@@ -5494,7 +6278,7 @@
         <v>9</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F9" s="1">
         <v>1</v>
@@ -5509,7 +6293,7 @@
         <v>2009</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C10" s="12" t="s">
         <v>29</v>
@@ -5518,7 +6302,7 @@
         <v>9</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F10" s="1">
         <v>0</v>
@@ -5533,7 +6317,7 @@
         <v>2010</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>29</v>
@@ -5542,7 +6326,7 @@
         <v>9</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F11" s="1">
         <v>0</v>
@@ -5557,7 +6341,7 @@
         <v>2011</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C12" s="12" t="s">
         <v>29</v>
@@ -5566,7 +6350,7 @@
         <v>9</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F12" s="1">
         <v>0</v>
@@ -5581,7 +6365,7 @@
         <v>2012</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C13" s="12" t="s">
         <v>29</v>
@@ -5590,7 +6374,7 @@
         <v>9</v>
       </c>
       <c r="E13" s="24" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>0</v>
@@ -5605,7 +6389,7 @@
         <v>2013</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C14" s="12" t="s">
         <v>29</v>
@@ -5614,7 +6398,7 @@
         <v>9</v>
       </c>
       <c r="E14" s="24" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>0</v>
@@ -5629,7 +6413,7 @@
         <v>2014</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C15" s="12" t="s">
         <v>29</v>
@@ -5638,7 +6422,7 @@
         <v>9</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F15" s="1">
         <v>0</v>
@@ -5653,7 +6437,7 @@
         <v>2015</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C16" s="12" t="s">
         <v>29</v>
@@ -5662,7 +6446,7 @@
         <v>9</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F16" s="1">
         <v>0</v>
@@ -5677,7 +6461,7 @@
         <v>2016</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C17" s="12" t="s">
         <v>29</v>
@@ -5686,7 +6470,7 @@
         <v>9</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F17" s="1">
         <v>1</v>
@@ -5701,7 +6485,7 @@
         <v>2017</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C18" s="12" t="s">
         <v>29</v>
@@ -5710,7 +6494,7 @@
         <v>9</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
@@ -5725,7 +6509,7 @@
         <v>2018</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C19" s="12" t="s">
         <v>29</v>
@@ -5734,7 +6518,7 @@
         <v>9</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="F19" s="1">
         <v>0</v>
@@ -5749,7 +6533,7 @@
         <v>2019</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C20" s="12" t="s">
         <v>29</v>
@@ -5758,7 +6542,7 @@
         <v>9</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
@@ -5773,7 +6557,7 @@
         <v>2020</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C21" s="12" t="s">
         <v>29</v>
@@ -5781,10 +6565,10 @@
       <c r="D21" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E21" s="24" t="s">
-        <v>114</v>
-      </c>
-      <c r="F21" s="1" t="s">
+      <c r="E21" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="F21" s="1">
         <v>0</v>
       </c>
       <c r="G21" s="3" t="str">
@@ -5797,7 +6581,7 @@
         <v>2021</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="C22" s="12" t="s">
         <v>29</v>
@@ -5806,13 +6590,13 @@
         <v>9</v>
       </c>
       <c r="E22" s="24" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G22" s="3" t="str">
-        <f t="shared" ref="G22:G24" si="2">IF(OR(AND(F22&gt;1,F22&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="G22:G26" si="2">IF(OR(AND(F22&gt;1,F22&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -5821,7 +6605,7 @@
         <v>2022</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="C23" s="12" t="s">
         <v>29</v>
@@ -5830,7 +6614,7 @@
         <v>9</v>
       </c>
       <c r="E23" s="24" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>0</v>
@@ -5845,7 +6629,7 @@
         <v>2023</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="C24" s="12" t="s">
         <v>29</v>
@@ -5854,12 +6638,60 @@
         <v>9</v>
       </c>
       <c r="E24" s="24" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G24" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="10">
+        <v>2024</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="F25" s="1">
+        <v>0</v>
+      </c>
+      <c r="G25" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="10">
+        <v>2025</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -5872,12 +6704,12 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="F3:F12 F15:F20">
-    <cfRule type="containsText" dxfId="8" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="32" priority="21" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F12 F15:F20">
-    <cfRule type="colorScale" priority="14">
+    <cfRule type="colorScale" priority="22">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -5889,11 +6721,62 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F13">
-    <cfRule type="containsText" dxfId="7" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="31" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F13))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F13">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F14">
+    <cfRule type="containsText" dxfId="30" priority="11" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F14))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F14">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F22:F24">
+    <cfRule type="containsText" dxfId="29" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F22))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F22:F24">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F26">
+    <cfRule type="containsText" dxfId="12" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F26))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F26">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5905,12 +6788,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F14">
-    <cfRule type="containsText" dxfId="6" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F14))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F14">
+  <conditionalFormatting sqref="F21">
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F21">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5922,12 +6805,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F21:F24">
-    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F21:F24">
+  <conditionalFormatting sqref="F25">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F25))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F25">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5966,7 +6849,7 @@
       <c r="C1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="32"/>
+      <c r="D1" s="33"/>
       <c r="E1" s="8" t="s">
         <v>3</v>
       </c>
@@ -5976,15 +6859,15 @@
       <c r="G1" s="2"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="33"/>
+      <c r="A2" s="32"/>
       <c r="B2" s="26" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>28</v>
@@ -5999,7 +6882,7 @@
         <v>2002</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C3" s="12" t="s">
         <v>29</v>
@@ -6008,7 +6891,7 @@
         <v>8</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F3" s="1">
         <v>1</v>
@@ -6024,7 +6907,7 @@
         <v>2003</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>29</v>
@@ -6033,7 +6916,7 @@
         <v>8</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="F4" s="1">
         <v>0</v>
@@ -6050,7 +6933,7 @@
         <v>2004</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>29</v>
@@ -6074,7 +6957,7 @@
         <v>2005</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>29</v>
@@ -6083,7 +6966,7 @@
         <v>8</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F6" s="1">
         <v>0</v>
@@ -6098,7 +6981,7 @@
         <v>2006</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>29</v>
@@ -6122,7 +7005,7 @@
         <v>2007</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>29</v>
@@ -6131,7 +7014,7 @@
         <v>8</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>0</v>
@@ -6146,7 +7029,7 @@
         <v>2008</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>29</v>
@@ -6155,7 +7038,7 @@
         <v>9</v>
       </c>
       <c r="E9" s="24" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>0</v>
@@ -6170,7 +7053,7 @@
         <v>2009</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C10" s="12" t="s">
         <v>29</v>
@@ -6179,7 +7062,7 @@
         <v>9</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>0</v>
@@ -6194,7 +7077,7 @@
         <v>2010</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>29</v>
@@ -6218,7 +7101,7 @@
         <v>2011</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C12" s="12" t="s">
         <v>29</v>
@@ -6242,7 +7125,7 @@
         <v>2012</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C13" s="12" t="s">
         <v>29</v>
@@ -6266,7 +7149,7 @@
         <v>2013</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C14" s="12" t="s">
         <v>29</v>
@@ -6290,7 +7173,7 @@
         <v>2014</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C15" s="12" t="s">
         <v>29</v>
@@ -6314,7 +7197,7 @@
         <v>2015</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C16" s="12" t="s">
         <v>29</v>
@@ -6338,7 +7221,7 @@
         <v>2016</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C17" s="12" t="s">
         <v>29</v>
@@ -6362,7 +7245,7 @@
         <v>2017</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C18" s="12" t="s">
         <v>29</v>
@@ -6386,7 +7269,7 @@
         <v>2018</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C19" s="12" t="s">
         <v>29</v>
@@ -6395,7 +7278,7 @@
         <v>9</v>
       </c>
       <c r="E19" s="24" t="s">
-        <v>45</v>
+        <v>117</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>0</v>
@@ -6410,7 +7293,7 @@
         <v>2019</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C20" s="12" t="s">
         <v>29</v>
@@ -6419,7 +7302,7 @@
         <v>9</v>
       </c>
       <c r="E20" s="24" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>0</v>
@@ -6434,7 +7317,7 @@
         <v>2020</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C21" s="12" t="s">
         <v>29</v>
@@ -6443,7 +7326,7 @@
         <v>9</v>
       </c>
       <c r="E21" s="24" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>0</v>
@@ -6458,7 +7341,7 @@
         <v>2021</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C22" s="12" t="s">
         <v>29</v>
@@ -6467,7 +7350,7 @@
         <v>9</v>
       </c>
       <c r="E22" s="24" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>0</v>
@@ -6482,7 +7365,7 @@
         <v>2022</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C23" s="12" t="s">
         <v>29</v>
@@ -6491,13 +7374,13 @@
         <v>9</v>
       </c>
       <c r="E23" s="24" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G23" s="3" t="str">
-        <f t="shared" ref="G23:G24" si="2">IF(OR(AND(F23&gt;1,F23&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="G23:G26" si="2">IF(OR(AND(F23&gt;1,F23&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -6506,7 +7389,7 @@
         <v>2023</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C24" s="12" t="s">
         <v>29</v>
@@ -6514,13 +7397,61 @@
       <c r="D24" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E24" s="24" t="s">
-        <v>121</v>
-      </c>
-      <c r="F24" s="1" t="s">
+      <c r="E24" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="F24" s="1">
         <v>0</v>
       </c>
       <c r="G24" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="10">
+        <v>2024</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E25" s="24" t="s">
+        <v>142</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G25" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="10">
+        <v>2025</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -6536,11 +7467,28 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="F3:F20 F22 F24">
-    <cfRule type="containsText" dxfId="4" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="28" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F20 F22 F24">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F21 F23">
+    <cfRule type="containsText" dxfId="27" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F23 F21">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6552,12 +7500,29 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F21 F23">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F23 F21">
+  <conditionalFormatting sqref="F26">
+    <cfRule type="containsText" dxfId="10" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F26))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F26">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F25">
+    <cfRule type="containsText" dxfId="9" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F25))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F25">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
